--- a/LongSubmerged10x/Data Sheets/General.xlsx
+++ b/LongSubmerged10x/Data Sheets/General.xlsx
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>-6e-07</v>
+        <v>-7.200000000000001e-08</v>
       </c>
     </row>
   </sheetData>
